--- a/src/test/resources/testdata/hybridFrameworkTestDriver.xlsx
+++ b/src/test/resources/testdata/hybridFrameworkTestDriver.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="89">
   <si>
     <t>Choose Test (Smoke/Regression/Custom/Negative)</t>
   </si>
@@ -760,7 +760,7 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="7" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="484">
+  <cellXfs count="507">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1283,6 +1283,29 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
@@ -1698,10 +1721,10 @@
         <v>11</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" t="s" s="483">
-        <v>59</v>
+        <v>87</v>
+      </c>
+      <c r="F2" t="s" s="488">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1720,7 +1743,7 @@
       <c r="E3" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F3" t="s" s="466">
+      <c r="F3" t="s" s="494">
         <v>59</v>
       </c>
     </row>
@@ -1738,10 +1761,10 @@
         <v>51</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" t="s" s="452">
-        <v>81</v>
+        <v>60</v>
+      </c>
+      <c r="F4" t="s" s="500">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1760,7 +1783,7 @@
       <c r="E5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" t="s" s="455">
+      <c r="F5" t="s" s="497">
         <v>59</v>
       </c>
     </row>
@@ -1780,7 +1803,7 @@
       <c r="E6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F6" t="s" s="469">
+      <c r="F6" t="s" s="503">
         <v>59</v>
       </c>
     </row>
@@ -1800,7 +1823,7 @@
       <c r="E7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F7" t="s" s="463">
+      <c r="F7" t="s" s="506">
         <v>59</v>
       </c>
     </row>
@@ -1879,8 +1902,8 @@
       <c r="F2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="481" t="s">
-        <v>59</v>
+      <c r="G2" s="485" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -1902,8 +1925,8 @@
       <c r="F3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="482" t="s">
-        <v>59</v>
+      <c r="G3" s="487" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +1990,7 @@
       <c r="E2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="430" t="s">
+      <c r="F2" s="489" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1987,7 +2010,7 @@
       <c r="E3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="460" t="s">
+      <c r="F3" s="490" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2003,7 +2026,7 @@
       <c r="E4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="461" t="s">
+      <c r="F4" s="491" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2021,7 +2044,7 @@
       <c r="E5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="464" t="s">
+      <c r="F5" s="492" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2039,7 +2062,7 @@
       <c r="E6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="465" t="s">
+      <c r="F6" s="493" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2123,7 +2146,7 @@
       <c r="H2" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="453" t="s">
+      <c r="I2" s="495" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2152,7 +2175,7 @@
       <c r="H3" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="454" t="s">
+      <c r="I3" s="496" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2216,8 +2239,8 @@
       <c r="E2" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="449" t="s">
-        <v>81</v>
+      <c r="F2" s="498" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="54" x14ac:dyDescent="0.45">
@@ -2236,8 +2259,8 @@
       <c r="E3" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="451" t="s">
-        <v>81</v>
+      <c r="F3" s="499" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2293,7 +2316,7 @@
       <c r="D2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="467" t="s">
+      <c r="E2" s="501" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2310,7 +2333,7 @@
       <c r="D3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="468" t="s">
+      <c r="E3" s="502" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2380,7 +2403,7 @@
       <c r="F2" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="459" t="s">
+      <c r="G2" s="504" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2403,7 +2426,7 @@
       <c r="F3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="462" t="s">
+      <c r="G3" s="505" t="s">
         <v>59</v>
       </c>
     </row>
